--- a/data/templates/listing_rules_template.xlsx
+++ b/data/templates/listing_rules_template.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H1"/>
+  <dimension ref="A1:J1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -429,30 +429,40 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>condition_type</t>
+          <t>variety_filter</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>condition_value</t>
+          <t>grade_filter</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>action</t>
+          <t>platform_filter</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
+          <t>stock_threshold</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>listing_strategy</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
           <t>active</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>priority</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>remark</t>
         </is>
